--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415052</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415051</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415057</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415053</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,6 +1097,103 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128753667</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95817</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stordalen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567694</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6719006</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95845</v>
+        <v>95851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95851</v>
+        <v>95858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95877</v>
+        <v>95882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95882</v>
+        <v>95885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95885</v>
+        <v>95895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95895</v>
+        <v>95902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35742-2025 artfynd.xlsx
+++ b/artfynd/A 35742-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>128753667</v>
       </c>
       <c r="B6" t="n">
-        <v>95902</v>
+        <v>95904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
